--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.66966</v>
+        <v>16.71662</v>
       </c>
       <c r="D2" t="n">
-        <v>16.48581</v>
+        <v>16.63078</v>
       </c>
       <c r="E2" t="n">
-        <v>16.74625</v>
+        <v>16.65968</v>
       </c>
       <c r="F2" t="n">
-        <v>42.66628</v>
+        <v>41.95015</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05134</v>
+        <v>0.04945</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86501</v>
+        <v>1.82568</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.63831</v>
+        <v>16.85994</v>
       </c>
       <c r="D3" t="n">
-        <v>16.94172</v>
+        <v>16.69858</v>
       </c>
       <c r="E3" t="n">
-        <v>16.61402</v>
+        <v>16.76633</v>
       </c>
       <c r="F3" t="n">
-        <v>42.28995</v>
+        <v>43.01553</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05056</v>
+        <v>0.04999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81891</v>
+        <v>1.85189</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.3756</v>
+        <v>16.66155</v>
       </c>
       <c r="D4" t="n">
-        <v>16.56654</v>
+        <v>16.65031</v>
       </c>
       <c r="E4" t="n">
-        <v>16.67162</v>
+        <v>16.65127</v>
       </c>
       <c r="F4" t="n">
-        <v>42.93978</v>
+        <v>43.14268</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05094</v>
+        <v>0.05028</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83371</v>
+        <v>1.81103</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.73892</v>
+        <v>16.68954</v>
       </c>
       <c r="D5" t="n">
-        <v>16.50792</v>
+        <v>16.57867</v>
       </c>
       <c r="E5" t="n">
-        <v>16.48057</v>
+        <v>16.62317</v>
       </c>
       <c r="F5" t="n">
-        <v>43.0616</v>
+        <v>42.83871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05029</v>
+        <v>0.05045</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8264</v>
+        <v>1.82653</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.03719</v>
+        <v>16.81953</v>
       </c>
       <c r="D6" t="n">
-        <v>16.69138</v>
+        <v>16.57428</v>
       </c>
       <c r="E6" t="n">
-        <v>16.74038</v>
+        <v>16.78787</v>
       </c>
       <c r="F6" t="n">
-        <v>41.86311</v>
+        <v>41.90626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05029</v>
+        <v>0.04979</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81985</v>
+        <v>1.80745</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.94562</v>
+        <v>17.0465</v>
       </c>
       <c r="D7" t="n">
-        <v>16.83234</v>
+        <v>16.88648</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76463</v>
+        <v>16.94725</v>
       </c>
       <c r="F7" t="n">
-        <v>42.83311</v>
+        <v>41.95341</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05092</v>
+        <v>0.04992</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83386</v>
+        <v>1.83909</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.79132</v>
+        <v>16.91227</v>
       </c>
       <c r="D8" t="n">
-        <v>16.63225</v>
+        <v>16.29171</v>
       </c>
       <c r="E8" t="n">
-        <v>17.26853</v>
+        <v>16.6657</v>
       </c>
       <c r="F8" t="n">
-        <v>41.92118</v>
+        <v>42.48365</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05123</v>
+        <v>0.05131</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79882</v>
+        <v>1.80819</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.98959</v>
+        <v>17.14361</v>
       </c>
       <c r="D9" t="n">
-        <v>16.59561</v>
+        <v>16.63872</v>
       </c>
       <c r="E9" t="n">
-        <v>16.3006</v>
+        <v>16.95684</v>
       </c>
       <c r="F9" t="n">
-        <v>43.21007</v>
+        <v>42.63271</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05035</v>
+        <v>0.05053</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80857</v>
+        <v>1.82674</v>
       </c>
     </row>
     <row r="10">
@@ -660,712 +660,1536 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.67224</v>
+        <v>17.23589</v>
       </c>
       <c r="D10" t="n">
-        <v>16.48145</v>
+        <v>16.51526</v>
       </c>
       <c r="E10" t="n">
-        <v>16.52694</v>
+        <v>16.59708</v>
       </c>
       <c r="F10" t="n">
-        <v>41.46125</v>
+        <v>42.54894</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05104</v>
+        <v>0.05135</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85307</v>
+        <v>1.80748</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.50619</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.99906</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.27144</v>
-      </c>
-      <c r="F11" t="n">
-        <v>42.70628</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.04995</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.83294</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.8935</v>
+        <v>16.83938</v>
       </c>
       <c r="D12" t="n">
-        <v>16.77723</v>
+        <v>16.30404</v>
       </c>
       <c r="E12" t="n">
-        <v>16.48909</v>
+        <v>16.40329</v>
       </c>
       <c r="F12" t="n">
-        <v>43.15506</v>
+        <v>42.28998</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05052</v>
+        <v>0.05119</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8426</v>
+        <v>1.79628</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.59597</v>
+        <v>16.88764</v>
       </c>
       <c r="D13" t="n">
-        <v>17.02985</v>
+        <v>16.68731</v>
       </c>
       <c r="E13" t="n">
-        <v>16.40117</v>
+        <v>16.88282</v>
       </c>
       <c r="F13" t="n">
-        <v>42.45112</v>
+        <v>41.90865</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05034</v>
+        <v>0.04953</v>
       </c>
       <c r="H13" t="n">
-        <v>1.81189</v>
+        <v>1.81758</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.62704</v>
+        <v>16.69972</v>
       </c>
       <c r="D14" t="n">
-        <v>16.77482</v>
+        <v>16.53552</v>
       </c>
       <c r="E14" t="n">
-        <v>16.53688</v>
+        <v>16.64475</v>
       </c>
       <c r="F14" t="n">
-        <v>42.75764</v>
+        <v>42.67235</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05104</v>
+        <v>0.0513</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81476</v>
+        <v>1.83924</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.47361</v>
+        <v>16.67427</v>
       </c>
       <c r="D15" t="n">
-        <v>16.6247</v>
+        <v>16.41203</v>
       </c>
       <c r="E15" t="n">
-        <v>16.47667</v>
+        <v>16.49544</v>
       </c>
       <c r="F15" t="n">
-        <v>42.45029</v>
+        <v>42.89611</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05061</v>
+        <v>0.05044</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82556</v>
+        <v>1.80517</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.92567</v>
+        <v>16.67964</v>
       </c>
       <c r="D16" t="n">
-        <v>16.53316</v>
+        <v>16.58539</v>
       </c>
       <c r="E16" t="n">
-        <v>16.43974</v>
+        <v>16.58705</v>
       </c>
       <c r="F16" t="n">
-        <v>41.55014</v>
+        <v>42.15181</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05022</v>
+        <v>0.05044</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81528</v>
+        <v>1.83698</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.79486</v>
+        <v>17.3208</v>
       </c>
       <c r="D17" t="n">
-        <v>16.71318</v>
+        <v>16.82708</v>
       </c>
       <c r="E17" t="n">
-        <v>16.391</v>
+        <v>16.98164</v>
       </c>
       <c r="F17" t="n">
-        <v>41.73505</v>
+        <v>42.44855</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04978</v>
+        <v>0.0508</v>
       </c>
       <c r="H17" t="n">
-        <v>1.83287</v>
+        <v>1.81059</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.7314</v>
+        <v>16.83376</v>
       </c>
       <c r="D18" t="n">
-        <v>16.71063</v>
+        <v>16.25366</v>
       </c>
       <c r="E18" t="n">
-        <v>16.68276</v>
+        <v>16.49399</v>
       </c>
       <c r="F18" t="n">
-        <v>42.70748</v>
+        <v>43.45818</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05121</v>
+        <v>0.04979</v>
       </c>
       <c r="H18" t="n">
-        <v>1.82541</v>
+        <v>1.79898</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.05042</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.28049</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.69313</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.40173</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.83713</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>16.25662</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.33007</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.54562</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.8556</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05122</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.82599</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="C20" t="n">
+        <v>16.75829</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.55803</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.66904</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.00021</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.82333</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.60683</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.09823</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.60127</v>
+        <v>16.007</v>
       </c>
       <c r="D22" t="n">
-        <v>1.10838</v>
+        <v>15.38056</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.46059</v>
+      </c>
+      <c r="F22" t="n">
+        <v>247.32573</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.60453</v>
+        <v>15.50656</v>
       </c>
       <c r="D23" t="n">
-        <v>1.11297</v>
+        <v>15.20839</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.21644</v>
+      </c>
+      <c r="F23" t="n">
+        <v>254.38341</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.60734</v>
+        <v>15.90771</v>
       </c>
       <c r="D24" t="n">
-        <v>1.11673</v>
+        <v>15.31525</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.44061</v>
+      </c>
+      <c r="F24" t="n">
+        <v>253.13137</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.60493</v>
+        <v>15.89402</v>
       </c>
       <c r="D25" t="n">
-        <v>1.12063</v>
+        <v>15.51357</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.85246</v>
+      </c>
+      <c r="F25" t="n">
+        <v>258.42677</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.60203</v>
+        <v>15.86767</v>
       </c>
       <c r="D26" t="n">
-        <v>1.11026</v>
+        <v>15.45379</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.64728</v>
+      </c>
+      <c r="F26" t="n">
+        <v>254.46465</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.60239</v>
+        <v>15.58006</v>
       </c>
       <c r="D27" t="n">
-        <v>1.10777</v>
+        <v>15.48371</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.54949</v>
+      </c>
+      <c r="F27" t="n">
+        <v>258.08333</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.60937</v>
+        <v>15.79134</v>
       </c>
       <c r="D28" t="n">
-        <v>1.11765</v>
+        <v>15.7216</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.76742</v>
+      </c>
+      <c r="F28" t="n">
+        <v>255.26847</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.65701</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.45629</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.64333</v>
+      </c>
+      <c r="F29" t="n">
+        <v>253.40928</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.60805</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.13235</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="C30" t="n">
+        <v>15.71443</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.3009</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.62216</v>
+      </c>
+      <c r="F30" t="n">
+        <v>254.40192</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.75726</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08037</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.6061299999999999</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.95317</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.11109</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.09161999999999999</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.12399</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.75313</v>
+        <v>16.64619</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08132</v>
+        <v>16.17112</v>
       </c>
       <c r="E32" t="n">
-        <v>0.60479</v>
+        <v>16.28553</v>
       </c>
       <c r="F32" t="n">
-        <v>0.96168</v>
+        <v>21.46565</v>
       </c>
       <c r="G32" t="n">
-        <v>0.10748</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09483</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.12532</v>
+        <v>34.00359</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.76938</v>
+        <v>16.69546</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07912</v>
+        <v>15.9722</v>
       </c>
       <c r="E33" t="n">
-        <v>0.60495</v>
+        <v>16.4518</v>
       </c>
       <c r="F33" t="n">
-        <v>0.96512</v>
+        <v>21.58752</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11058</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09384000000000001</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.12604</v>
+        <v>34.30883</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.74618</v>
+        <v>16.72963</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08105999999999999</v>
+        <v>15.98055</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6118400000000001</v>
+        <v>16.33582</v>
       </c>
       <c r="F34" t="n">
-        <v>0.976</v>
+        <v>21.52887</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11087</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09282</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.12553</v>
+        <v>34.17907</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.74433</v>
+        <v>16.78454</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08069</v>
+        <v>16.01398</v>
       </c>
       <c r="E35" t="n">
-        <v>0.61025</v>
+        <v>16.14558</v>
       </c>
       <c r="F35" t="n">
-        <v>0.99433</v>
+        <v>21.92784</v>
       </c>
       <c r="G35" t="n">
-        <v>0.10701</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09181</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.12738</v>
+        <v>33.10902</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.76461</v>
+        <v>16.50893</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08162</v>
+        <v>15.96043</v>
       </c>
       <c r="E36" t="n">
-        <v>0.60711</v>
+        <v>16.13098</v>
       </c>
       <c r="F36" t="n">
-        <v>0.95309</v>
+        <v>22.27616</v>
       </c>
       <c r="G36" t="n">
-        <v>0.10997</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00741</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09327000000000001</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.1269</v>
+        <v>34.18885</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.75325</v>
+        <v>16.60923</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08254</v>
+        <v>16.00526</v>
       </c>
       <c r="E37" t="n">
-        <v>0.60442</v>
+        <v>16.36971</v>
       </c>
       <c r="F37" t="n">
-        <v>0.97127</v>
+        <v>22.14933</v>
       </c>
       <c r="G37" t="n">
-        <v>0.10923</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09292</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.12714</v>
+        <v>33.86401</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.74572</v>
+        <v>17.13996</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08099000000000001</v>
+        <v>16.3715</v>
       </c>
       <c r="E38" t="n">
-        <v>0.61282</v>
+        <v>16.42363</v>
       </c>
       <c r="F38" t="n">
-        <v>0.95925</v>
+        <v>21.98089</v>
       </c>
       <c r="G38" t="n">
-        <v>0.10976</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00771</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09492</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.1271</v>
+        <v>34.09673</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.60235</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.23328</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.45054</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.13759</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.29144</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>0.75657</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.08141</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.60126</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.97418</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.10729</v>
-      </c>
-      <c r="H39" t="n">
+      <c r="C40" t="n">
+        <v>17.15524</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.02602</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.26902</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.8825</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.52831</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.75447</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.04865</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.56048</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.38625</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.92936</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.57243</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.144</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.49557</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.95179</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.688</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.97506</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.03898</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.59925</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.09595</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.15767</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.91026</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.09941</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.41042</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.66447</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.25081</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.76586</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.59563</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.68522</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.73931</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.90164</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.75353</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.51963</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.50153</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.79642</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.4123</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.80995</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.74871</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.39896</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.95632</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.07937</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.58974</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.59521</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.41549</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.56762</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.26633</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.47509</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.31629</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.42021</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.89379</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.3087</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.60075</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.09726</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6044</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.11989</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.62076</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.12647</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.59801</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.11358</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60247</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.11431</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.61866</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.09735</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6153</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.11252</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.59736</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.14039</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.62316</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.1185</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.61505</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.08065</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.60234</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.09685</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.61027</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.11624</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.59796</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.12315</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.60868</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.11467</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.60593</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.11536</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.59917</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.11362</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5911</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.1152</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.59774</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.1053</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.74457</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.07908999999999999</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6010799999999999</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.94755</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.11119</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09357</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12665</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.75652</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08115</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.60711</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.95159</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10871</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09282</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.74695</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.60041</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10853</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09296</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12586</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.75132</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.60751</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.96446</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10924</v>
+      </c>
+      <c r="H75" t="n">
         <v>0.00758</v>
       </c>
-      <c r="I39" t="n">
-        <v>0.09209000000000001</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.12618</v>
+      <c r="I75" t="n">
+        <v>0.09533</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12663</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.75121</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08144999999999999</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.61289</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.95135</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11146</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09352000000000001</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12438</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.74769</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08032</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.60719</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.9922299999999999</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10937</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09686</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12948</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.75784</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08031000000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.60116</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.97163</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10902</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09297999999999999</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12306</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.75927</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08118</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.59645</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.9599</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.11046</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09372</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12543</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.75058</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08139</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6022999999999999</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.96512</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.11058</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09322</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12738</v>
       </c>
     </row>
   </sheetData>
